--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Nifty 50 ETF.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Nifty 50 ETF.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\mumchfnp01\RatingFinance\Factseet Mandates\ICICI PRUDENTIAL FACTSHEET\2025\Feb\Portfolio stage 8\Riskometer updated Portfolio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\mumchfnp01\RatingFinance\Factseet Mandates\ICICI PRUDENTIAL FACTSHEET\2025\June\Portfolio stage 8\Riskometer updated portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9878739B-4C2F-4C67-8C4B-2D10FC6CE0D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FCC3B91-860F-497A-AF7C-08E0C8DF1830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="164">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -28,7 +28,7 @@
     <t>ICICI Prudential Nifty 50 ETF</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -109,28 +109,34 @@
     <t>Telecom - Services</t>
   </si>
   <si>
+    <t>Larsen &amp; Toubro Ltd.</t>
+  </si>
+  <si>
+    <t>INE018A01030</t>
+  </si>
+  <si>
+    <t>Construction</t>
+  </si>
+  <si>
+    <t>ITC Ltd.</t>
+  </si>
+  <si>
+    <t>INE154A01025</t>
+  </si>
+  <si>
+    <t>Diversified Fmcg</t>
+  </si>
+  <si>
     <t>Tata Consultancy Services Ltd.</t>
   </si>
   <si>
     <t>INE467B01029</t>
   </si>
   <si>
-    <t>Larsen &amp; Toubro Ltd.</t>
-  </si>
-  <si>
-    <t>INE018A01030</t>
-  </si>
-  <si>
-    <t>Construction</t>
-  </si>
-  <si>
-    <t>ITC Ltd.</t>
-  </si>
-  <si>
-    <t>INE154A01025</t>
-  </si>
-  <si>
-    <t>Diversified Fmcg</t>
+    <t>Axis Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE238A01034</t>
   </si>
   <si>
     <t>State Bank Of India</t>
@@ -139,12 +145,6 @@
     <t>INE062A01020</t>
   </si>
   <si>
-    <t>Axis Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE238A01034</t>
-  </si>
-  <si>
     <t>Kotak Mahindra Bank Ltd.</t>
   </si>
   <si>
@@ -190,6 +190,15 @@
     <t>INE860A01027</t>
   </si>
   <si>
+    <t>Zomato Ltd.</t>
+  </si>
+  <si>
+    <t>INE758T01015</t>
+  </si>
+  <si>
+    <t>Retailing</t>
+  </si>
+  <si>
     <t>Maruti Suzuki India Ltd.</t>
   </si>
   <si>
@@ -220,6 +229,24 @@
     <t>Consumer Durables</t>
   </si>
   <si>
+    <t>Bharat Electronics Ltd.</t>
+  </si>
+  <si>
+    <t>INE263A01024</t>
+  </si>
+  <si>
+    <t>Aerospace &amp; Defense</t>
+  </si>
+  <si>
+    <t>Tata Steel Ltd.</t>
+  </si>
+  <si>
+    <t>INE081A01020</t>
+  </si>
+  <si>
+    <t>Ferrous Metals</t>
+  </si>
+  <si>
     <t>Power Grid Corporation Of India Ltd.</t>
   </si>
   <si>
@@ -241,16 +268,25 @@
     <t>INE849A01020</t>
   </si>
   <si>
-    <t>Retailing</t>
-  </si>
-  <si>
-    <t>Tata Steel Ltd.</t>
-  </si>
-  <si>
-    <t>INE081A01020</t>
-  </si>
-  <si>
-    <t>Ferrous Metals</t>
+    <t>Bajaj Finserv Ltd.</t>
+  </si>
+  <si>
+    <t>INE918I01026</t>
+  </si>
+  <si>
+    <t>Adani Ports and Special Economic Zone Ltd.</t>
+  </si>
+  <si>
+    <t>INE742F01042</t>
+  </si>
+  <si>
+    <t>Transport Infrastructure</t>
+  </si>
+  <si>
+    <t>Asian Paints Ltd.</t>
+  </si>
+  <si>
+    <t>INE021A01026</t>
   </si>
   <si>
     <t>Tech Mahindra Ltd.</t>
@@ -259,19 +295,28 @@
     <t>INE669C01036</t>
   </si>
   <si>
-    <t>Bharat Electronics Ltd.</t>
-  </si>
-  <si>
-    <t>INE263A01024</t>
-  </si>
-  <si>
-    <t>Aerospace &amp; Defense</t>
-  </si>
-  <si>
-    <t>Asian Paints Ltd.</t>
-  </si>
-  <si>
-    <t>INE021A01026</t>
+    <t>Grasim Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE047A01021</t>
+  </si>
+  <si>
+    <t>Bajaj Auto Ltd.</t>
+  </si>
+  <si>
+    <t>INE917I01010</t>
+  </si>
+  <si>
+    <t>JSW Steel Ltd.</t>
+  </si>
+  <si>
+    <t>INE019A01038</t>
+  </si>
+  <si>
+    <t>Jio Financial Services Ltd</t>
+  </si>
+  <si>
+    <t>INE758E01017</t>
   </si>
   <si>
     <t>Oil &amp; Natural Gas Corporation Ltd.</t>
@@ -283,28 +328,13 @@
     <t>Oil</t>
   </si>
   <si>
-    <t>Bajaj Auto Ltd.</t>
-  </si>
-  <si>
-    <t>INE917I01010</t>
-  </si>
-  <si>
-    <t>Bajaj Finserv Ltd.</t>
-  </si>
-  <si>
-    <t>INE918I01026</t>
-  </si>
-  <si>
-    <t>Grasim Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE047A01021</t>
-  </si>
-  <si>
-    <t>JSW Steel Ltd.</t>
-  </si>
-  <si>
-    <t>INE019A01038</t>
+    <t>Hindalco Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE038A01020</t>
+  </si>
+  <si>
+    <t>Non - Ferrous Metals</t>
   </si>
   <si>
     <t>Coal India Ltd.</t>
@@ -316,63 +346,69 @@
     <t>Consumable Fuels</t>
   </si>
   <si>
+    <t>Shriram Finance Ltd.</t>
+  </si>
+  <si>
+    <t>INE721A01047</t>
+  </si>
+  <si>
+    <t>Nestle India Ltd.</t>
+  </si>
+  <si>
+    <t>INE239A01024</t>
+  </si>
+  <si>
+    <t>Food Products</t>
+  </si>
+  <si>
+    <t>HDFC Life Insurance Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE795G01014</t>
+  </si>
+  <si>
+    <t>Insurance</t>
+  </si>
+  <si>
+    <t>Cipla Ltd.</t>
+  </si>
+  <si>
+    <t>INE059A01026</t>
+  </si>
+  <si>
+    <t>SBI Life Insurance Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE123W01016</t>
+  </si>
+  <si>
+    <t>Dr. Reddy's Laboratories Ltd.</t>
+  </si>
+  <si>
+    <t>INE089A01031</t>
+  </si>
+  <si>
+    <t>Eicher Motors Ltd.</t>
+  </si>
+  <si>
+    <t>INE066A01021</t>
+  </si>
+  <si>
+    <t>Tata Consumer Products Ltd.</t>
+  </si>
+  <si>
+    <t>INE192A01025</t>
+  </si>
+  <si>
+    <t>Agricultural Food &amp; Other Products</t>
+  </si>
+  <si>
     <t>Wipro Ltd.</t>
   </si>
   <si>
     <t>INE075A01022</t>
   </si>
   <si>
-    <t>Hindalco Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE038A01020</t>
-  </si>
-  <si>
-    <t>Non - Ferrous Metals</t>
-  </si>
-  <si>
-    <t>Nestle India Ltd.</t>
-  </si>
-  <si>
-    <t>INE239A01024</t>
-  </si>
-  <si>
-    <t>Food Products</t>
-  </si>
-  <si>
-    <t>Cipla Ltd.</t>
-  </si>
-  <si>
-    <t>INE059A01026</t>
-  </si>
-  <si>
-    <t>Adani Ports and Special Economic Zone Ltd.</t>
-  </si>
-  <si>
-    <t>INE742F01042</t>
-  </si>
-  <si>
-    <t>Transport Infrastructure</t>
-  </si>
-  <si>
-    <t>Shriram Finance Ltd.</t>
-  </si>
-  <si>
-    <t>INE721A01047</t>
-  </si>
-  <si>
-    <t>Dr. Reddy's Laboratories Ltd.</t>
-  </si>
-  <si>
-    <t>INE089A01031</t>
-  </si>
-  <si>
-    <t>Eicher Motors Ltd.</t>
-  </si>
-  <si>
-    <t>INE066A01021</t>
-  </si>
-  <si>
     <t>Apollo Hospitals Enterprise Ltd.</t>
   </si>
   <si>
@@ -382,28 +418,19 @@
     <t>Healthcare Services</t>
   </si>
   <si>
-    <t>HDFC Life Insurance Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE795G01014</t>
-  </si>
-  <si>
-    <t>Insurance</t>
-  </si>
-  <si>
-    <t>Tata Consumer Products Ltd.</t>
-  </si>
-  <si>
-    <t>INE192A01025</t>
-  </si>
-  <si>
-    <t>Agricultural Food &amp; Other Products</t>
-  </si>
-  <si>
-    <t>SBI Life Insurance Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE123W01016</t>
+    <t>Adani Enterprises Ltd.</t>
+  </si>
+  <si>
+    <t>INE423A01024</t>
+  </si>
+  <si>
+    <t>Metals &amp; Minerals Trading</t>
+  </si>
+  <si>
+    <t>Hero Motocorp Ltd.</t>
+  </si>
+  <si>
+    <t>INE158A01026</t>
   </si>
   <si>
     <t>IndusInd Bank Ltd.</t>
@@ -412,42 +439,6 @@
     <t>INE095A01012</t>
   </si>
   <si>
-    <t>Britannia Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE216A01030</t>
-  </si>
-  <si>
-    <t>Adani Enterprises Ltd.</t>
-  </si>
-  <si>
-    <t>INE423A01024</t>
-  </si>
-  <si>
-    <t>Metals &amp; Minerals Trading</t>
-  </si>
-  <si>
-    <t>Hero Motocorp Ltd.</t>
-  </si>
-  <si>
-    <t>INE158A01026</t>
-  </si>
-  <si>
-    <t>Bharat Petroleum Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE029A01011</t>
-  </si>
-  <si>
-    <t>ITC Hotels Ltd</t>
-  </si>
-  <si>
-    <t>INE379A01028</t>
-  </si>
-  <si>
-    <t>Leisure Services</t>
-  </si>
-  <si>
     <t>Unlisted</t>
   </si>
   <si>
@@ -505,7 +496,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -819,13 +810,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>103</xdr:row>
+      <xdr:row>102</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>113</xdr:row>
+      <xdr:row>112</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -849,7 +840,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="20231100"/>
+          <a:off x="666750" y="20040600"/>
           <a:ext cx="3571875" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -866,13 +857,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>118</xdr:row>
+      <xdr:row>117</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>128</xdr:row>
+      <xdr:row>127</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -896,7 +887,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="23088600"/>
+          <a:off x="666750" y="22898100"/>
           <a:ext cx="3571875" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1232,7 +1223,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J117"/>
+  <dimension ref="A1:J116"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10" style="24" customWidth="1" collapsed="1"/>
@@ -1332,10 +1323,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="12">
-        <v>2321416.1000000006</v>
+        <v>3000505.9999999995</v>
       </c>
       <c r="H5" s="13">
-        <v>0.99885173388269988</v>
+        <v>0.99851465110020021</v>
       </c>
       <c r="I5" s="12" t="s">
         <v>13</v>
@@ -1369,10 +1360,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="12">
-        <v>2321416.1000000006</v>
+        <v>3000505.9999999995</v>
       </c>
       <c r="H7" s="13">
-        <v>0.99885173388269988</v>
+        <v>0.99851465110020021</v>
       </c>
       <c r="I7" s="12" t="s">
         <v>13</v>
@@ -1395,13 +1386,13 @@
         <v>17</v>
       </c>
       <c r="F8" s="17">
-        <v>16725309</v>
+        <v>20387465</v>
       </c>
       <c r="G8" s="18">
-        <v>284121.19</v>
+        <v>396515.81</v>
       </c>
       <c r="H8" s="19">
-        <v>0.12225078617519999</v>
+        <v>0.13195335909299999</v>
       </c>
       <c r="I8" s="18" t="s">
         <v>13</v>
@@ -1424,13 +1415,13 @@
         <v>17</v>
       </c>
       <c r="F9" s="17">
-        <v>15519341</v>
+        <v>18916265</v>
       </c>
       <c r="G9" s="18">
-        <v>194426.3</v>
+        <v>273491.36</v>
       </c>
       <c r="H9" s="19">
-        <v>8.3657146544200006E-2</v>
+        <v>9.1013025772999995E-2</v>
       </c>
       <c r="I9" s="18" t="s">
         <v>13</v>
@@ -1453,13 +1444,13 @@
         <v>22</v>
       </c>
       <c r="F10" s="17">
-        <v>14931031</v>
+        <v>18157760</v>
       </c>
       <c r="G10" s="18">
-        <v>188892.47</v>
+        <v>258003.61</v>
       </c>
       <c r="H10" s="19">
-        <v>8.1276067300999996E-2</v>
+        <v>8.5858979992799997E-2</v>
       </c>
       <c r="I10" s="18" t="s">
         <v>13</v>
@@ -1482,13 +1473,13 @@
         <v>25</v>
       </c>
       <c r="F11" s="17">
-        <v>7922915</v>
+        <v>9647615</v>
       </c>
       <c r="G11" s="18">
-        <v>148934.96</v>
+        <v>150763.28</v>
       </c>
       <c r="H11" s="19">
-        <v>6.4083273581099998E-2</v>
+        <v>5.0171319080199998E-2</v>
       </c>
       <c r="I11" s="18" t="s">
         <v>13</v>
@@ -1511,13 +1502,13 @@
         <v>28</v>
       </c>
       <c r="F12" s="17">
-        <v>5899160</v>
+        <v>7189703</v>
       </c>
       <c r="G12" s="18">
-        <v>95938.04</v>
+        <v>133455.26999999999</v>
       </c>
       <c r="H12" s="19">
-        <v>4.1279922888200003E-2</v>
+        <v>4.4411523377000002E-2</v>
       </c>
       <c r="I12" s="18" t="s">
         <v>13</v>
@@ -1537,16 +1528,16 @@
         <v>13</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F13" s="17">
-        <v>2247628</v>
+        <v>3146093</v>
       </c>
       <c r="G13" s="18">
-        <v>92431.45</v>
+        <v>115622.06</v>
       </c>
       <c r="H13" s="19">
-        <v>3.9771118197200001E-2</v>
+        <v>3.8476950521200003E-2</v>
       </c>
       <c r="I13" s="18" t="s">
         <v>13</v>
@@ -1557,25 +1548,25 @@
     </row>
     <row r="14" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="15" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D14" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F14" s="17">
-        <v>2589070</v>
+        <v>24946971</v>
       </c>
       <c r="G14" s="18">
-        <v>92362.48</v>
+        <v>104290.81</v>
       </c>
       <c r="H14" s="19">
-        <v>3.9741441999000003E-2</v>
+        <v>3.4706113488900001E-2</v>
       </c>
       <c r="I14" s="18" t="s">
         <v>13</v>
@@ -1586,25 +1577,25 @@
     </row>
     <row r="15" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D15" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="F15" s="17">
-        <v>20449104</v>
+        <v>2737106</v>
       </c>
       <c r="G15" s="18">
-        <v>91509.74</v>
+        <v>94796.93</v>
       </c>
       <c r="H15" s="19">
-        <v>3.9374527671399998E-2</v>
+        <v>3.1546720281299998E-2</v>
       </c>
       <c r="I15" s="18" t="s">
         <v>13</v>
@@ -1627,13 +1618,13 @@
         <v>17</v>
       </c>
       <c r="F16" s="17">
-        <v>8464280</v>
+        <v>7658119</v>
       </c>
       <c r="G16" s="18">
-        <v>65420.42</v>
+        <v>91300.09</v>
       </c>
       <c r="H16" s="19">
-        <v>2.8148895817700002E-2</v>
+        <v>3.0383034565500001E-2</v>
       </c>
       <c r="I16" s="18" t="s">
         <v>13</v>
@@ -1656,13 +1647,13 @@
         <v>17</v>
       </c>
       <c r="F17" s="17">
-        <v>6272564</v>
+        <v>10296300</v>
       </c>
       <c r="G17" s="18">
-        <v>61853.75</v>
+        <v>83636.84</v>
       </c>
       <c r="H17" s="19">
-        <v>2.6614240090200001E-2</v>
+        <v>2.78328422312E-2</v>
       </c>
       <c r="I17" s="18" t="s">
         <v>13</v>
@@ -1685,13 +1676,13 @@
         <v>17</v>
       </c>
       <c r="F18" s="17">
-        <v>3229848</v>
+        <v>3940595</v>
       </c>
       <c r="G18" s="18">
-        <v>61409.1</v>
+        <v>81755.520000000004</v>
       </c>
       <c r="H18" s="19">
-        <v>2.6422917464600001E-2</v>
+        <v>2.7206772633799999E-2</v>
       </c>
       <c r="I18" s="18" t="s">
         <v>13</v>
@@ -1714,13 +1705,13 @@
         <v>45</v>
       </c>
       <c r="F19" s="17">
-        <v>1947117</v>
+        <v>2374839</v>
       </c>
       <c r="G19" s="18">
-        <v>58215.88</v>
+        <v>70694.210000000006</v>
       </c>
       <c r="H19" s="19">
-        <v>2.50489486471E-2</v>
+        <v>2.3525766798299999E-2</v>
       </c>
       <c r="I19" s="18" t="s">
         <v>13</v>
@@ -1743,13 +1734,13 @@
         <v>48</v>
       </c>
       <c r="F20" s="17">
-        <v>615486</v>
+        <v>700819</v>
       </c>
       <c r="G20" s="18">
-        <v>48531.69</v>
+        <v>64338.69</v>
       </c>
       <c r="H20" s="19">
-        <v>2.0882065349999999E-2</v>
+        <v>2.1410763583700001E-2</v>
       </c>
       <c r="I20" s="18" t="s">
         <v>13</v>
@@ -1769,16 +1760,16 @@
         <v>13</v>
       </c>
       <c r="E21" s="16" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F21" s="17">
-        <v>1952364</v>
+        <v>2378488</v>
       </c>
       <c r="G21" s="18">
-        <v>48199.96</v>
+        <v>55854.03</v>
       </c>
       <c r="H21" s="19">
-        <v>2.0739329592400001E-2</v>
+        <v>1.8587220714799998E-2</v>
       </c>
       <c r="I21" s="18" t="s">
         <v>13</v>
@@ -1801,13 +1792,13 @@
         <v>53</v>
       </c>
       <c r="F22" s="17">
-        <v>2374379</v>
+        <v>2889432</v>
       </c>
       <c r="G22" s="18">
-        <v>41407.980000000003</v>
+        <v>48473.11</v>
       </c>
       <c r="H22" s="19">
-        <v>1.7816897461699999E-2</v>
+        <v>1.6130982747400002E-2</v>
       </c>
       <c r="I22" s="18" t="s">
         <v>13</v>
@@ -1830,13 +1821,13 @@
         <v>25</v>
       </c>
       <c r="F23" s="17">
-        <v>2328442</v>
+        <v>2842643</v>
       </c>
       <c r="G23" s="18">
-        <v>40176.1</v>
+        <v>46522.7</v>
       </c>
       <c r="H23" s="19">
-        <v>1.7286847948399998E-2</v>
+        <v>1.5481921235500001E-2</v>
       </c>
       <c r="I23" s="18" t="s">
         <v>13</v>
@@ -1856,16 +1847,16 @@
         <v>13</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="F24" s="17">
-        <v>289370</v>
+        <v>18618854</v>
       </c>
       <c r="G24" s="18">
-        <v>35623.33</v>
+        <v>44370.59</v>
       </c>
       <c r="H24" s="19">
-        <v>1.53278961653E-2</v>
+        <v>1.47657375766E-2</v>
       </c>
       <c r="I24" s="18" t="s">
         <v>13</v>
@@ -1876,25 +1867,25 @@
     </row>
     <row r="25" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B25" s="15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D25" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E25" s="16" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="F25" s="17">
-        <v>10414764</v>
+        <v>351732</v>
       </c>
       <c r="G25" s="18">
-        <v>33743.839999999997</v>
+        <v>43329.87</v>
       </c>
       <c r="H25" s="19">
-        <v>1.45191950258E-2</v>
+        <v>1.44194046022E-2</v>
       </c>
       <c r="I25" s="18" t="s">
         <v>13</v>
@@ -1914,16 +1905,16 @@
         <v>13</v>
       </c>
       <c r="E26" s="16" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="F26" s="17">
-        <v>4610590</v>
+        <v>12707641</v>
       </c>
       <c r="G26" s="18">
-        <v>33016.43</v>
+        <v>42430.81</v>
       </c>
       <c r="H26" s="19">
-        <v>1.4206207302600001E-2</v>
+        <v>1.41202135383E-2</v>
       </c>
       <c r="I26" s="18" t="s">
         <v>13</v>
@@ -1934,25 +1925,25 @@
     </row>
     <row r="27" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B27" s="15" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D27" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="F27" s="17">
-        <v>909928</v>
+        <v>5592797</v>
       </c>
       <c r="G27" s="18">
-        <v>31758.76</v>
+        <v>40240.17</v>
       </c>
       <c r="H27" s="19">
-        <v>1.36650609479E-2</v>
+        <v>1.3391207785500001E-2</v>
       </c>
       <c r="I27" s="18" t="s">
         <v>13</v>
@@ -1972,16 +1963,16 @@
         <v>13</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="F28" s="17">
-        <v>9963206</v>
+        <v>1105319</v>
       </c>
       <c r="G28" s="18">
-        <v>30054.01</v>
+        <v>39294.089999999997</v>
       </c>
       <c r="H28" s="19">
-        <v>1.29315463947E-2</v>
+        <v>1.30763693079E-2</v>
       </c>
       <c r="I28" s="18" t="s">
         <v>13</v>
@@ -1992,25 +1983,25 @@
     </row>
     <row r="29" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B29" s="15" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D29" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F29" s="17">
-        <v>250816</v>
+        <v>9598270</v>
       </c>
       <c r="G29" s="18">
-        <v>28812.36</v>
+        <v>36914.949999999997</v>
       </c>
       <c r="H29" s="19">
-        <v>1.23972930761E-2</v>
+        <v>1.2284634131600001E-2</v>
       </c>
       <c r="I29" s="18" t="s">
         <v>13</v>
@@ -2021,25 +2012,25 @@
     </row>
     <row r="30" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B30" s="15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D30" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F30" s="17">
-        <v>488296</v>
+        <v>22160869</v>
       </c>
       <c r="G30" s="18">
-        <v>28092.65</v>
+        <v>35683.43</v>
       </c>
       <c r="H30" s="19">
-        <v>1.2087618485E-2</v>
+        <v>1.18748063348E-2</v>
       </c>
       <c r="I30" s="18" t="s">
         <v>13</v>
@@ -2050,25 +2041,25 @@
     </row>
     <row r="31" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B31" s="15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D31" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E31" s="16" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="F31" s="17">
-        <v>18224991</v>
+        <v>12146385</v>
       </c>
       <c r="G31" s="18">
-        <v>24534.48</v>
+        <v>35194.15</v>
       </c>
       <c r="H31" s="19">
-        <v>1.05566201113E-2</v>
+        <v>1.17119827149E-2</v>
       </c>
       <c r="I31" s="18" t="s">
         <v>13</v>
@@ -2088,16 +2079,16 @@
         <v>13</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="F32" s="17">
-        <v>1396436</v>
+        <v>311793</v>
       </c>
       <c r="G32" s="18">
-        <v>23382.62</v>
+        <v>34952</v>
       </c>
       <c r="H32" s="19">
-        <v>1.00610013559E-2</v>
+        <v>1.16313995323E-2</v>
       </c>
       <c r="I32" s="18" t="s">
         <v>13</v>
@@ -2108,25 +2099,25 @@
     </row>
     <row r="33" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B33" s="15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D33" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E33" s="16" t="s">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="F33" s="17">
-        <v>7866202</v>
+        <v>595583</v>
       </c>
       <c r="G33" s="18">
-        <v>23020.44</v>
+        <v>33611.730000000003</v>
       </c>
       <c r="H33" s="19">
-        <v>9.9051636666000007E-3</v>
+        <v>1.1185381683500001E-2</v>
       </c>
       <c r="I33" s="18" t="s">
         <v>13</v>
@@ -2146,16 +2137,16 @@
         <v>13</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="F34" s="17">
-        <v>994622</v>
+        <v>1458035</v>
       </c>
       <c r="G34" s="18">
-        <v>22884.26</v>
+        <v>29414.400000000001</v>
       </c>
       <c r="H34" s="19">
-        <v>9.8465685577000008E-3</v>
+        <v>9.7885854430000002E-3</v>
       </c>
       <c r="I34" s="18" t="s">
         <v>13</v>
@@ -2178,13 +2169,13 @@
         <v>86</v>
       </c>
       <c r="F35" s="17">
-        <v>8531208</v>
+        <v>1977725</v>
       </c>
       <c r="G35" s="18">
-        <v>22403.81</v>
+        <v>28336.84</v>
       </c>
       <c r="H35" s="19">
-        <v>9.6398420188000006E-3</v>
+        <v>9.4299927764999996E-3</v>
       </c>
       <c r="I35" s="18" t="s">
         <v>13</v>
@@ -2204,16 +2195,16 @@
         <v>13</v>
       </c>
       <c r="E36" s="16" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="F36" s="17">
-        <v>243933</v>
+        <v>1212239</v>
       </c>
       <c r="G36" s="18">
-        <v>21582.7</v>
+        <v>27385.69</v>
       </c>
       <c r="H36" s="19">
-        <v>9.2865373497000008E-3</v>
+        <v>9.1134670936999992E-3</v>
       </c>
       <c r="I36" s="18" t="s">
         <v>13</v>
@@ -2233,16 +2224,16 @@
         <v>13</v>
       </c>
       <c r="E37" s="16" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="F37" s="17">
-        <v>1203105</v>
+        <v>1699872</v>
       </c>
       <c r="G37" s="18">
-        <v>20887.11</v>
+        <v>26754.29</v>
       </c>
       <c r="H37" s="19">
-        <v>8.9872410375999995E-3</v>
+        <v>8.9033484835000006E-3</v>
       </c>
       <c r="I37" s="18" t="s">
         <v>13</v>
@@ -2262,16 +2253,16 @@
         <v>13</v>
       </c>
       <c r="E38" s="16" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="F38" s="17">
-        <v>817260</v>
+        <v>1028652</v>
       </c>
       <c r="G38" s="18">
-        <v>20503.830000000002</v>
+        <v>26187.42</v>
       </c>
       <c r="H38" s="19">
-        <v>8.8223245056000005E-3</v>
+        <v>8.7147043014000006E-3</v>
       </c>
       <c r="I38" s="18" t="s">
         <v>13</v>
@@ -2291,16 +2282,16 @@
         <v>13</v>
       </c>
       <c r="E39" s="16" t="s">
-        <v>76</v>
+        <v>45</v>
       </c>
       <c r="F39" s="17">
-        <v>2110884</v>
+        <v>297208</v>
       </c>
       <c r="G39" s="18">
-        <v>19947.849999999999</v>
+        <v>25580.69</v>
       </c>
       <c r="H39" s="19">
-        <v>8.5830991520999995E-3</v>
+        <v>8.5127954252000003E-3</v>
       </c>
       <c r="I39" s="18" t="s">
         <v>13</v>
@@ -2320,16 +2311,16 @@
         <v>13</v>
       </c>
       <c r="E40" s="16" t="s">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="F40" s="17">
-        <v>4988931</v>
+        <v>2542690</v>
       </c>
       <c r="G40" s="18">
-        <v>19751.18</v>
+        <v>25261.63</v>
       </c>
       <c r="H40" s="19">
-        <v>8.4984765933000007E-3</v>
+        <v>8.4066179723000008E-3</v>
       </c>
       <c r="I40" s="18" t="s">
         <v>13</v>
@@ -2340,25 +2331,25 @@
     </row>
     <row r="41" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B41" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="C41" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="C41" s="16" t="s">
-        <v>99</v>
-      </c>
       <c r="D41" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E41" s="16" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="F41" s="17">
-        <v>6228168</v>
+        <v>8778609</v>
       </c>
       <c r="G41" s="18">
-        <v>19425.66</v>
+        <v>25163.88</v>
       </c>
       <c r="H41" s="19">
-        <v>8.3584128553000001E-3</v>
+        <v>8.3740885232000007E-3</v>
       </c>
       <c r="I41" s="18" t="s">
         <v>13</v>
@@ -2369,25 +2360,25 @@
     </row>
     <row r="42" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B42" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="C42" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="C42" s="16" t="s">
+      <c r="D42" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E42" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="D42" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="E42" s="16" t="s">
-        <v>102</v>
-      </c>
       <c r="F42" s="17">
-        <v>3197401</v>
+        <v>10409496</v>
       </c>
       <c r="G42" s="18">
-        <v>19002.150000000001</v>
+        <v>24920.33</v>
       </c>
       <c r="H42" s="19">
-        <v>8.1761862833999999E-3</v>
+        <v>8.2930394456999998E-3</v>
       </c>
       <c r="I42" s="18" t="s">
         <v>13</v>
@@ -2398,25 +2389,25 @@
     </row>
     <row r="43" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B43" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="C43" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="C43" s="16" t="s">
+      <c r="D43" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E43" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="D43" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="E43" s="16" t="s">
-        <v>105</v>
-      </c>
       <c r="F43" s="17">
-        <v>787626</v>
+        <v>3880143</v>
       </c>
       <c r="G43" s="18">
-        <v>18219.36</v>
+        <v>24580.71</v>
       </c>
       <c r="H43" s="19">
-        <v>7.8393698251999992E-3</v>
+        <v>8.1800199931E-3</v>
       </c>
       <c r="I43" s="18" t="s">
         <v>13</v>
@@ -2427,25 +2418,25 @@
     </row>
     <row r="44" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B44" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="C44" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="C44" s="16" t="s">
+      <c r="D44" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E44" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="D44" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="E44" s="16" t="s">
-        <v>53</v>
-      </c>
       <c r="F44" s="17">
-        <v>1209162</v>
+        <v>6087168</v>
       </c>
       <c r="G44" s="18">
-        <v>17888.34</v>
+        <v>24184.32</v>
       </c>
       <c r="H44" s="19">
-        <v>7.6969395642999998E-3</v>
+        <v>8.0481085012999998E-3</v>
       </c>
       <c r="I44" s="18" t="s">
         <v>13</v>
@@ -2465,16 +2456,16 @@
         <v>13</v>
       </c>
       <c r="E45" s="16" t="s">
-        <v>110</v>
+        <v>48</v>
       </c>
       <c r="F45" s="17">
-        <v>1621241</v>
+        <v>3750947</v>
       </c>
       <c r="G45" s="18">
-        <v>17823.11</v>
+        <v>23981.68</v>
       </c>
       <c r="H45" s="19">
-        <v>7.6688726017999998E-3</v>
+        <v>7.9806735389999998E-3</v>
       </c>
       <c r="I45" s="18" t="s">
         <v>13</v>
@@ -2485,25 +2476,25 @@
     </row>
     <row r="46" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B46" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="C46" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="C46" s="16" t="s">
+      <c r="D46" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E46" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="D46" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="E46" s="16" t="s">
-        <v>48</v>
-      </c>
       <c r="F46" s="17">
-        <v>3074133</v>
+        <v>960917</v>
       </c>
       <c r="G46" s="18">
-        <v>16715.599999999999</v>
+        <v>23025.49</v>
       </c>
       <c r="H46" s="19">
-        <v>7.1923366271000001E-3</v>
+        <v>7.6624706344999996E-3</v>
       </c>
       <c r="I46" s="18" t="s">
         <v>13</v>
@@ -2523,16 +2514,16 @@
         <v>13</v>
       </c>
       <c r="E47" s="16" t="s">
-        <v>53</v>
+        <v>115</v>
       </c>
       <c r="F47" s="17">
-        <v>1341701</v>
+        <v>2869133</v>
       </c>
       <c r="G47" s="18">
-        <v>16333.2</v>
+        <v>22288.86</v>
       </c>
       <c r="H47" s="19">
-        <v>7.0277987388000004E-3</v>
+        <v>7.4173333652000004E-3</v>
       </c>
       <c r="I47" s="18" t="s">
         <v>13</v>
@@ -2543,25 +2534,25 @@
     </row>
     <row r="48" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B48" s="15" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C48" s="16" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D48" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E48" s="16" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="F48" s="17">
-        <v>302620</v>
+        <v>1507681</v>
       </c>
       <c r="G48" s="18">
-        <v>15718.99</v>
+        <v>22098.080000000002</v>
       </c>
       <c r="H48" s="19">
-        <v>6.7635183612000001E-3</v>
+        <v>7.3538451984999998E-3</v>
       </c>
       <c r="I48" s="18" t="s">
         <v>13</v>
@@ -2572,25 +2563,25 @@
     </row>
     <row r="49" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B49" s="15" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C49" s="16" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D49" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E49" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F49" s="17">
-        <v>222563</v>
+        <v>1201135</v>
       </c>
       <c r="G49" s="18">
-        <v>15157.65</v>
+        <v>21766.97</v>
       </c>
       <c r="H49" s="19">
-        <v>6.5219867234999999E-3</v>
+        <v>7.2436577214000002E-3</v>
       </c>
       <c r="I49" s="18" t="s">
         <v>13</v>
@@ -2610,16 +2601,16 @@
         <v>13</v>
       </c>
       <c r="E50" s="16" t="s">
-        <v>122</v>
+        <v>53</v>
       </c>
       <c r="F50" s="17">
-        <v>2350975</v>
+        <v>1634811</v>
       </c>
       <c r="G50" s="18">
-        <v>15000.4</v>
+        <v>20454.759999999998</v>
       </c>
       <c r="H50" s="19">
-        <v>6.4543256802999998E-3</v>
+        <v>6.8069777380000002E-3</v>
       </c>
       <c r="I50" s="18" t="s">
         <v>13</v>
@@ -2630,25 +2621,25 @@
     </row>
     <row r="51" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B51" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="C51" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="C51" s="16" t="s">
-        <v>124</v>
-      </c>
       <c r="D51" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E51" s="16" t="s">
-        <v>125</v>
+        <v>45</v>
       </c>
       <c r="F51" s="17">
-        <v>1430898</v>
+        <v>368306</v>
       </c>
       <c r="G51" s="18">
-        <v>14661.7</v>
+        <v>19643.599999999999</v>
       </c>
       <c r="H51" s="19">
-        <v>6.3085908927000001E-3</v>
+        <v>6.5370382195999999E-3</v>
       </c>
       <c r="I51" s="18" t="s">
         <v>13</v>
@@ -2659,25 +2650,25 @@
     </row>
     <row r="52" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B52" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="C52" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="D52" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E52" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="C52" s="16" t="s">
-        <v>127</v>
-      </c>
-      <c r="D52" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="E52" s="16" t="s">
-        <v>122</v>
-      </c>
       <c r="F52" s="17">
-        <v>984348</v>
+        <v>1745188</v>
       </c>
       <c r="G52" s="18">
-        <v>14603.79</v>
+        <v>19307.009999999998</v>
       </c>
       <c r="H52" s="19">
-        <v>6.2836735570999998E-3</v>
+        <v>6.4250270967000003E-3</v>
       </c>
       <c r="I52" s="18" t="s">
         <v>13</v>
@@ -2688,25 +2679,25 @@
     </row>
     <row r="53" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B53" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="C53" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="C53" s="16" t="s">
-        <v>129</v>
-      </c>
       <c r="D53" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E53" s="16" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F53" s="17">
-        <v>1452936</v>
+        <v>7612156</v>
       </c>
       <c r="G53" s="18">
-        <v>14401.5</v>
+        <v>19005.27</v>
       </c>
       <c r="H53" s="19">
-        <v>6.1966328420999996E-3</v>
+        <v>6.3246134295000004E-3</v>
       </c>
       <c r="I53" s="18" t="s">
         <v>13</v>
@@ -2717,25 +2708,25 @@
     </row>
     <row r="54" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B54" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="C54" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="C54" s="16" t="s">
+      <c r="D54" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E54" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="D54" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="E54" s="16" t="s">
-        <v>105</v>
-      </c>
       <c r="F54" s="17">
-        <v>259091</v>
+        <v>270749</v>
       </c>
       <c r="G54" s="18">
-        <v>13290.46</v>
+        <v>18628.88</v>
       </c>
       <c r="H54" s="19">
-        <v>5.7185779900000002E-3</v>
+        <v>6.1993575795E-3</v>
       </c>
       <c r="I54" s="18" t="s">
         <v>13</v>
@@ -2758,13 +2749,13 @@
         <v>134</v>
       </c>
       <c r="F55" s="17">
-        <v>547433</v>
+        <v>698026</v>
       </c>
       <c r="G55" s="18">
-        <v>12524.17</v>
+        <v>17589.560000000001</v>
       </c>
       <c r="H55" s="19">
-        <v>5.3888611007000004E-3</v>
+        <v>5.8534905E-3</v>
       </c>
       <c r="I55" s="18" t="s">
         <v>13</v>
@@ -2787,13 +2778,13 @@
         <v>45</v>
       </c>
       <c r="F56" s="17">
-        <v>285102</v>
+        <v>347881</v>
       </c>
       <c r="G56" s="18">
-        <v>12371</v>
+        <v>14991.24</v>
       </c>
       <c r="H56" s="19">
-        <v>5.3229555872000003E-3</v>
+        <v>4.9888161456999999E-3</v>
       </c>
       <c r="I56" s="18" t="s">
         <v>13</v>
@@ -2813,16 +2804,16 @@
         <v>13</v>
       </c>
       <c r="E57" s="16" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F57" s="17">
-        <v>4257304</v>
+        <v>1764892</v>
       </c>
       <c r="G57" s="18">
-        <v>11115.82</v>
+        <v>14418.29</v>
       </c>
       <c r="H57" s="19">
-        <v>4.7828806220999998E-3</v>
+        <v>4.7981486484999997E-3</v>
       </c>
       <c r="I57" s="18" t="s">
         <v>13</v>
@@ -2833,562 +2824,562 @@
     </row>
     <row r="58" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B58" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J58" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="59" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B59" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="C58" s="16" t="s">
+      <c r="C59" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D59" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E59" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F59" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G59" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="D58" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="E58" s="16" t="s">
+      <c r="H59" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="I59" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J59" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="60" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B60" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J60" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="61" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B61" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="F58" s="17">
-        <v>2044819</v>
-      </c>
-      <c r="G58" s="18">
-        <v>3332.03</v>
-      </c>
-      <c r="H58" s="19">
-        <v>1.4336955545E-3</v>
-      </c>
-      <c r="I58" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="J58" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="59" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J59" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="60" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B60" s="10" t="s">
+      <c r="C61" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D61" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E61" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F61" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G61" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="H61" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="I61" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J61" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="62" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B62" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J62" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="63" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B63" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C63" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D63" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E63" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F63" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G63" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="H63" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="I63" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J63" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="64" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B64" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J64" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="65" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B65" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="C60" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D60" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E60" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F60" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G60" s="12" t="s">
+      <c r="C65" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D65" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E65" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F65" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G65" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="H65" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="I65" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J65" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="66" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B66" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J66" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="67" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B67" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="H60" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="I60" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J60" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="61" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B61" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J61" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="62" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B62" s="10" t="s">
+      <c r="C67" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D67" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E67" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F67" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G67" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="H67" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="I67" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J67" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="68" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B68" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J68" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="69" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B69" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="C62" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D62" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E62" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F62" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G62" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="H62" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="I62" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J62" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="63" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B63" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J63" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="64" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B64" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C64" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D64" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E64" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F64" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G64" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="H64" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="I64" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J64" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="65" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B65" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J65" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="66" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B66" s="10" t="s">
+      <c r="C69" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D69" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E69" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F69" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G69" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="H69" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="I69" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J69" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="70" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B70" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J70" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="71" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B71" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="C66" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D66" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E66" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F66" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G66" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="H66" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="I66" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J66" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="67" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B67" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J67" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="68" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B68" s="10" t="s">
+      <c r="C71" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D71" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E71" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F71" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G71" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="H71" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="I71" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J71" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="72" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B72" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J72" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="73" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B73" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="C68" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D68" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E68" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F68" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G68" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="H68" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="I68" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J68" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="69" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B69" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J69" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="70" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B70" s="10" t="s">
+      <c r="C73" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D73" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E73" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F73" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G73" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="H73" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="I73" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J73" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="74" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B74" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J74" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="75" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B75" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="C70" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D70" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E70" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F70" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G70" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="H70" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="I70" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J70" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="71" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B71" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J71" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="72" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B72" s="10" t="s">
+      <c r="C75" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D75" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E75" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F75" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G75" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="H75" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="I75" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J75" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="76" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B76" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J76" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="77" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B77" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="C72" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D72" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E72" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F72" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G72" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="H72" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="I72" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J72" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="73" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B73" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J73" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="74" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B74" s="10" t="s">
+      <c r="C77" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D77" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E77" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F77" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G77" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="H77" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="I77" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J77" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="78" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B78" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J78" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="79" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B79" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="C74" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D74" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E74" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F74" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G74" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="H74" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="I74" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J74" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="75" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B75" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J75" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="76" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B76" s="10" t="s">
+      <c r="C79" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D79" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E79" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F79" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G79" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="H79" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="I79" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J79" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="80" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B80" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J80" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="81" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B81" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="C76" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D76" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E76" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F76" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G76" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="H76" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="I76" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J76" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="77" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B77" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J77" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="78" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B78" s="10" t="s">
+      <c r="C81" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D81" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E81" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F81" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G81" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="H81" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="I81" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J81" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="82" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B82" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J82" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="83" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B83" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="C78" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D78" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E78" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F78" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G78" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="H78" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="I78" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J78" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="79" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B79" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J79" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="80" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B80" s="10" t="s">
+      <c r="C83" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D83" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E83" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F83" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G83" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="H83" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="I83" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J83" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="84" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B84" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J84" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="85" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B85" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="C80" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D80" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E80" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F80" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G80" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="H80" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="I80" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J80" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="81" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B81" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J81" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="82" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B82" s="10" t="s">
+      <c r="C85" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D85" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E85" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F85" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G85" s="12">
+        <v>3262.25</v>
+      </c>
+      <c r="H85" s="13">
+        <v>1.0856183658000001E-3</v>
+      </c>
+      <c r="I85" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J85" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="86" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B86" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J86" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="87" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B87" s="20" t="s">
         <v>153</v>
       </c>
-      <c r="C82" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D82" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E82" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F82" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G82" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="H82" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="I82" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J82" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="83" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B83" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J83" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="84" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B84" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="C84" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D84" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E84" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F84" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G84" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="H84" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="I84" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J84" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="85" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B85" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J85" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="86" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B86" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="C86" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D86" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E86" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F86" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G86" s="12">
-        <v>3891.18</v>
-      </c>
-      <c r="H86" s="13">
-        <v>1.6742848856999999E-3</v>
-      </c>
-      <c r="I86" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J86" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="87" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B87" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J87" s="14" t="s">
+      <c r="C87" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="D87" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="E87" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F87" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G87" s="21">
+        <v>1201.1780254999176</v>
+      </c>
+      <c r="H87" s="22">
+        <v>3.9973053113195417E-4</v>
+      </c>
+      <c r="I87" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="J87" s="23" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="88" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B88" s="20" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C88" s="21" t="s">
         <v>13</v>
@@ -3403,10 +3394,10 @@
         <v>13</v>
       </c>
       <c r="G88" s="21">
-        <v>-1222.512212799862</v>
+        <v>3004969.4280254999</v>
       </c>
       <c r="H88" s="22">
-        <v>-5.2601877080578102E-4</v>
+        <v>0.99999999999713174</v>
       </c>
       <c r="I88" s="21" t="s">
         <v>13</v>
@@ -3415,38 +3406,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="89" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B89" s="20" t="s">
-        <v>157</v>
-      </c>
-      <c r="C89" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="D89" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="E89" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="F89" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G89" s="21">
-        <v>2324084.7677871999</v>
-      </c>
-      <c r="H89" s="22">
-        <v>0.99999999999759415</v>
-      </c>
-      <c r="I89" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="J89" s="23" t="s">
-        <v>13</v>
-      </c>
+    <row r="91" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B91" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C91" s="5"/>
+      <c r="D91" s="5"/>
+      <c r="E91" s="5"/>
+      <c r="F91" s="5"/>
+      <c r="G91" s="5"/>
+      <c r="H91" s="5"/>
+      <c r="I91" s="5"/>
     </row>
     <row r="92" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B92" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C92" s="5"/>
       <c r="D92" s="5"/>
@@ -3454,11 +3428,10 @@
       <c r="F92" s="5"/>
       <c r="G92" s="5"/>
       <c r="H92" s="5"/>
-      <c r="I92" s="5"/>
-    </row>
-    <row r="93" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B93" s="1" t="s">
-        <v>159</v>
+    </row>
+    <row r="93" spans="2:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B93" s="6" t="s">
+        <v>157</v>
       </c>
       <c r="C93" s="5"/>
       <c r="D93" s="5"/>
@@ -3469,7 +3442,7 @@
     </row>
     <row r="94" spans="2:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B94" s="6" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C94" s="5"/>
       <c r="D94" s="5"/>
@@ -3480,7 +3453,7 @@
     </row>
     <row r="95" spans="2:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B95" s="6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C95" s="5"/>
       <c r="D95" s="5"/>
@@ -3489,54 +3462,43 @@
       <c r="G95" s="5"/>
       <c r="H95" s="5"/>
     </row>
-    <row r="96" spans="2:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B96" s="6" t="s">
+    <row r="97" spans="2:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B97" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="C97" s="5"/>
+      <c r="D97" s="5"/>
+      <c r="E97" s="5"/>
+      <c r="F97" s="5"/>
+      <c r="G97" s="5"/>
+      <c r="H97" s="5"/>
+    </row>
+    <row r="100" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B100" s="24" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="115" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B115" s="24" t="s">
         <v>162</v>
-      </c>
-      <c r="C96" s="5"/>
-      <c r="D96" s="5"/>
-      <c r="E96" s="5"/>
-      <c r="F96" s="5"/>
-      <c r="G96" s="5"/>
-      <c r="H96" s="5"/>
-    </row>
-    <row r="98" spans="2:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B98" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="C98" s="5"/>
-      <c r="D98" s="5"/>
-      <c r="E98" s="5"/>
-      <c r="F98" s="5"/>
-      <c r="G98" s="5"/>
-      <c r="H98" s="5"/>
-    </row>
-    <row r="101" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B101" s="24" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="116" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B116" s="24" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="117" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B117" s="24" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="B93:H93"/>
     <mergeCell ref="B94:H94"/>
     <mergeCell ref="B95:H95"/>
-    <mergeCell ref="B96:H96"/>
-    <mergeCell ref="B98:H98"/>
+    <mergeCell ref="B97:H97"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B92:I92"/>
-    <mergeCell ref="B93:H93"/>
+    <mergeCell ref="B91:I91"/>
+    <mergeCell ref="B92:H92"/>
   </mergeCells>
   <printOptions headings="1" gridLines="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
